--- a/form_reporting_templates/Form-1IN.xlsx
+++ b/form_reporting_templates/Form-1IN.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\echassot\Desktop\iotc-reference-forms\form_reporting_templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\echassot\Desktop\repositories\data-reporting\iotc-reference-forms\form_reporting_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734E3F71-5768-4D2B-952E-B5C6F3EE0A5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D217FBA-98A4-46F5-A3D7-6C019FB7A6D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <workbookProtection workbookAlgorithmName="SHA-512" workbookHashValue="Z3raniWjLRXszYCbzXa/TU1R8wd1kHrHNccmNn7mHkAZRDJmvrP7BMraCIbrDBSr6tBMzuhQ6TxYUg6cyC/1Bg==" workbookSaltValue="C01nC0I7gdRYfsDcA3RybQ==" workbookSpinCount="100000" lockStructure="1"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="32">
   <si>
     <t>Name</t>
   </si>
@@ -100,12 +100,6 @@
   </si>
   <si>
     <t>Whale sharks</t>
-  </si>
-  <si>
-    <t>National legislations?</t>
-  </si>
-  <si>
-    <t>Legislation reference</t>
   </si>
   <si>
     <t>Original data</t>
@@ -244,7 +238,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="36">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -439,36 +433,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -534,35 +498,7 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color indexed="64"/>
       </left>
       <right style="thin">
@@ -600,32 +536,6 @@
         <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -687,6 +597,19 @@
       <right/>
       <top/>
       <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -696,7 +619,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -716,22 +639,22 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -773,7 +696,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="23" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -788,57 +711,25 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -855,30 +746,21 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="34" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="28" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="0" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -922,25 +804,22 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="30" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1267,55 +1146,55 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:H27"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="2.85546875" customWidth="1"/>
-    <col min="3" max="3" width="27.140625" customWidth="1"/>
-    <col min="4" max="4" width="28.5703125" customWidth="1"/>
-    <col min="6" max="6" width="27.140625" customWidth="1"/>
-    <col min="7" max="7" width="28.5703125" customWidth="1"/>
-    <col min="8" max="8" width="2.85546875" customWidth="1"/>
+    <col min="1" max="2" width="2.88671875" customWidth="1"/>
+    <col min="3" max="3" width="27.109375" customWidth="1"/>
+    <col min="4" max="4" width="28.5546875" customWidth="1"/>
+    <col min="6" max="6" width="27.109375" customWidth="1"/>
+    <col min="7" max="7" width="28.5546875" customWidth="1"/>
+    <col min="8" max="8" width="2.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="71" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="73"/>
-    </row>
-    <row r="3" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="74"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="76"/>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:8" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="2" spans="2:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="60" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="62"/>
+    </row>
+    <row r="3" spans="2:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="65"/>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B4" s="28"/>
       <c r="C4" s="29" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="30" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E4" s="31"/>
       <c r="F4" s="29" t="s">
         <v>8</v>
       </c>
       <c r="G4" s="32" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H4" s="33"/>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B5" s="17"/>
       <c r="C5" s="20"/>
       <c r="D5" s="20"/>
@@ -1324,7 +1203,7 @@
       <c r="G5" s="20"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:8" ht="18" x14ac:dyDescent="0.35">
       <c r="B6" s="17"/>
       <c r="C6" s="24" t="s">
         <v>6</v>
@@ -1335,7 +1214,7 @@
       <c r="G6" s="20"/>
       <c r="H6" s="16"/>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="17"/>
       <c r="C7" s="20"/>
       <c r="D7" s="20"/>
@@ -1344,20 +1223,20 @@
       <c r="G7" s="20"/>
       <c r="H7" s="16"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B8" s="17"/>
-      <c r="C8" s="70" t="s">
-        <v>33</v>
-      </c>
-      <c r="D8" s="70"/>
+      <c r="C8" s="59" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="59"/>
       <c r="E8" s="20"/>
-      <c r="F8" s="70" t="s">
-        <v>25</v>
-      </c>
-      <c r="G8" s="70"/>
+      <c r="F8" s="59" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" s="59"/>
       <c r="H8" s="16"/>
     </row>
-    <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:8" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="17"/>
       <c r="C9" s="27" t="s">
         <v>1</v>
@@ -1370,20 +1249,20 @@
       <c r="G9" s="3"/>
       <c r="H9" s="16"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B10" s="17"/>
       <c r="C10" s="18" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D10" s="3"/>
       <c r="E10" s="20"/>
       <c r="F10" s="20" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="16"/>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B11" s="17"/>
       <c r="C11" s="18"/>
       <c r="D11" s="19"/>
@@ -1392,29 +1271,29 @@
       <c r="G11" s="19"/>
       <c r="H11" s="16"/>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" s="17"/>
       <c r="C12" s="18" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" s="66"/>
+        <v>25</v>
+      </c>
+      <c r="D12" s="55"/>
       <c r="E12" s="20"/>
       <c r="F12" s="20"/>
       <c r="G12" s="20"/>
       <c r="H12" s="16"/>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" s="17"/>
       <c r="C13" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="66"/>
+      <c r="D13" s="55"/>
       <c r="E13" s="20"/>
       <c r="F13" s="20"/>
       <c r="G13" s="20"/>
       <c r="H13" s="16"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B14" s="17"/>
       <c r="C14" s="20"/>
       <c r="D14" s="20"/>
@@ -1423,7 +1302,7 @@
       <c r="G14" s="20"/>
       <c r="H14" s="16"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" s="17"/>
       <c r="C15" s="23"/>
       <c r="D15" s="23"/>
@@ -1432,7 +1311,7 @@
       <c r="G15" s="23"/>
       <c r="H15" s="16"/>
     </row>
-    <row r="16" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:8" ht="18" x14ac:dyDescent="0.35">
       <c r="B16" s="17"/>
       <c r="C16" s="24" t="s">
         <v>2</v>
@@ -1443,7 +1322,7 @@
       <c r="G16" s="20"/>
       <c r="H16" s="16"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="17"/>
       <c r="C17" s="20"/>
       <c r="D17" s="20"/>
@@ -1452,7 +1331,7 @@
       <c r="G17" s="20"/>
       <c r="H17" s="16"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="17"/>
       <c r="C18" s="18" t="s">
         <v>3</v>
@@ -1463,10 +1342,10 @@
       <c r="G18" s="25"/>
       <c r="H18" s="16"/>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="17"/>
-      <c r="C19" s="56" t="s">
-        <v>24</v>
+      <c r="C19" s="48" t="s">
+        <v>22</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="20"/>
@@ -1474,10 +1353,10 @@
       <c r="G19" s="26"/>
       <c r="H19" s="16"/>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="17"/>
-      <c r="C20" s="55" t="s">
-        <v>31</v>
+      <c r="C20" s="47" t="s">
+        <v>29</v>
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="20"/>
@@ -1485,7 +1364,7 @@
       <c r="G20" s="20"/>
       <c r="H20" s="16"/>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="17"/>
       <c r="C21" s="18"/>
       <c r="D21" s="19"/>
@@ -1494,7 +1373,7 @@
       <c r="G21" s="20"/>
       <c r="H21" s="16"/>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="17"/>
       <c r="C22" s="21"/>
       <c r="D22" s="22"/>
@@ -1503,7 +1382,7 @@
       <c r="G22" s="23"/>
       <c r="H22" s="16"/>
     </row>
-    <row r="23" spans="2:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:8" ht="18" x14ac:dyDescent="0.35">
       <c r="B23" s="17"/>
       <c r="C23" s="24" t="s">
         <v>5</v>
@@ -1514,7 +1393,7 @@
       <c r="G23" s="20"/>
       <c r="H23" s="16"/>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="17"/>
       <c r="C24" s="20"/>
       <c r="D24" s="20"/>
@@ -1523,16 +1402,16 @@
       <c r="G24" s="20"/>
       <c r="H24" s="16"/>
     </row>
-    <row r="25" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:8" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B25" s="17"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="68"/>
-      <c r="F25" s="68"/>
-      <c r="G25" s="69"/>
+      <c r="C25" s="56"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="58"/>
       <c r="H25" s="16"/>
     </row>
-    <row r="26" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="13"/>
       <c r="C26" s="14"/>
       <c r="D26" s="14"/>
@@ -1541,7 +1420,7 @@
       <c r="G26" s="14"/>
       <c r="H26" s="15"/>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="C27" s="1"/>
       <c r="D27" s="2"/>
     </row>
@@ -1569,525 +1448,485 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O55"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:K55"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.85546875" customWidth="1"/>
-    <col min="2" max="2" width="15.7109375" style="9" customWidth="1"/>
-    <col min="3" max="3" width="11.42578125" style="12" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" style="54" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.42578125" style="9" customWidth="1"/>
-    <col min="6" max="6" width="11.42578125" style="36" customWidth="1"/>
-    <col min="7" max="9" width="21.42578125" style="47" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="21.42578125" style="41" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.42578125" style="42" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="20" style="43" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="21.42578125" style="45" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.42578125" style="42" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="20" style="43" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="2.88671875" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" style="9" customWidth="1"/>
+    <col min="3" max="3" width="11.44140625" style="12" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" style="46" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.44140625" style="9" customWidth="1"/>
+    <col min="6" max="6" width="11.44140625" style="36" customWidth="1"/>
+    <col min="7" max="11" width="21.44140625" style="39" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" ht="7.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1"/>
       <c r="C1"/>
       <c r="D1"/>
       <c r="E1"/>
-      <c r="F1" s="49"/>
+      <c r="F1" s="41"/>
       <c r="G1"/>
       <c r="H1"/>
       <c r="I1"/>
       <c r="J1"/>
       <c r="K1"/>
-      <c r="L1"/>
-      <c r="M1"/>
-      <c r="N1"/>
-      <c r="O1"/>
-    </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="71" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
-      <c r="J2" s="72"/>
-      <c r="K2" s="72"/>
-      <c r="L2" s="72"/>
-      <c r="M2" s="72"/>
-      <c r="N2" s="72"/>
-      <c r="O2" s="73"/>
-    </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="50"/>
-      <c r="B3" s="74"/>
-      <c r="C3" s="75"/>
-      <c r="D3" s="75"/>
-      <c r="E3" s="75"/>
-      <c r="F3" s="75"/>
-      <c r="G3" s="75"/>
-      <c r="H3" s="75"/>
-      <c r="I3" s="75"/>
-      <c r="J3" s="75"/>
-      <c r="K3" s="75"/>
-      <c r="L3" s="75"/>
-      <c r="M3" s="75"/>
-      <c r="N3" s="75"/>
-      <c r="O3" s="76"/>
-    </row>
-    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="77" t="s">
+    </row>
+    <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="60" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="61"/>
+      <c r="D2" s="61"/>
+      <c r="E2" s="61"/>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
+      <c r="J2" s="61"/>
+      <c r="K2" s="61"/>
+    </row>
+    <row r="3" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="42"/>
+      <c r="B3" s="63"/>
+      <c r="C3" s="64"/>
+      <c r="D3" s="64"/>
+      <c r="E3" s="64"/>
+      <c r="F3" s="64"/>
+      <c r="G3" s="64"/>
+      <c r="H3" s="64"/>
+      <c r="I3" s="64"/>
+      <c r="J3" s="64"/>
+      <c r="K3" s="64"/>
+    </row>
+    <row r="4" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="78"/>
-      <c r="D4" s="51" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" s="79" t="s">
+      <c r="C4" s="67"/>
+      <c r="D4" s="43" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="68" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="80"/>
-      <c r="G4" s="48" t="s">
+      <c r="F4" s="69"/>
+      <c r="G4" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="48" t="s">
+      <c r="H4" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="48" t="s">
+      <c r="I4" s="40" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="81" t="s">
+      <c r="J4" s="70" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="82"/>
-      <c r="L4" s="83"/>
-      <c r="M4" s="82" t="s">
+      <c r="K4" s="40" t="s">
         <v>20</v>
       </c>
-      <c r="N4" s="82"/>
-      <c r="O4" s="83"/>
-    </row>
-    <row r="5" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="57" t="s">
+    </row>
+    <row r="5" spans="1:11" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B5" s="49" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="65" t="s">
+      <c r="D5" s="54" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="64" t="s">
+      <c r="F5" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="59" t="s">
+      <c r="G5" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="59" t="s">
+      <c r="H5" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="I5" s="59" t="s">
+      <c r="I5" s="51" t="s">
         <v>16</v>
       </c>
-      <c r="J5" s="60" t="s">
+      <c r="J5" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="K5" s="61" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5" s="62" t="s">
-        <v>22</v>
-      </c>
-      <c r="M5" s="63" t="s">
+      <c r="K5" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="N5" s="61" t="s">
-        <v>21</v>
-      </c>
-      <c r="O5" s="62" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="7"/>
       <c r="C6" s="8"/>
-      <c r="D6" s="52"/>
+      <c r="D6" s="44"/>
       <c r="E6" s="10"/>
       <c r="F6" s="34"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
       <c r="J6" s="38"/>
-      <c r="K6" s="39"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="44"/>
-      <c r="N6" s="39"/>
-      <c r="O6" s="40"/>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="K6" s="38"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B7" s="4"/>
       <c r="C7" s="5"/>
-      <c r="D7" s="53"/>
+      <c r="D7" s="45"/>
       <c r="E7" s="11"/>
       <c r="F7" s="35"/>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" s="4"/>
       <c r="C8" s="5"/>
-      <c r="D8" s="53"/>
+      <c r="D8" s="45"/>
       <c r="E8" s="11"/>
       <c r="F8" s="35"/>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B9" s="4"/>
       <c r="C9" s="5"/>
-      <c r="D9" s="53"/>
+      <c r="D9" s="45"/>
       <c r="E9" s="11"/>
       <c r="F9" s="35"/>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B10" s="4"/>
       <c r="C10" s="5"/>
-      <c r="D10" s="53"/>
+      <c r="D10" s="45"/>
       <c r="E10" s="11"/>
       <c r="F10" s="35"/>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B11" s="4"/>
       <c r="C11" s="5"/>
-      <c r="D11" s="53"/>
+      <c r="D11" s="45"/>
       <c r="E11" s="11"/>
       <c r="F11" s="35"/>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B12" s="4"/>
       <c r="C12" s="5"/>
-      <c r="D12" s="53"/>
+      <c r="D12" s="45"/>
       <c r="E12" s="11"/>
       <c r="F12" s="35"/>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B13" s="4"/>
       <c r="C13" s="5"/>
-      <c r="D13" s="53"/>
+      <c r="D13" s="45"/>
       <c r="E13" s="11"/>
       <c r="F13" s="35"/>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B14" s="4"/>
       <c r="C14" s="5"/>
-      <c r="D14" s="53"/>
+      <c r="D14" s="45"/>
       <c r="E14" s="11"/>
       <c r="F14" s="35"/>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B15" s="4"/>
       <c r="C15" s="5"/>
-      <c r="D15" s="53"/>
+      <c r="D15" s="45"/>
       <c r="E15" s="11"/>
       <c r="F15" s="35"/>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B16" s="4"/>
       <c r="C16" s="5"/>
-      <c r="D16" s="53"/>
+      <c r="D16" s="45"/>
       <c r="E16" s="11"/>
       <c r="F16" s="35"/>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17" s="4"/>
       <c r="C17" s="5"/>
-      <c r="D17" s="53"/>
+      <c r="D17" s="45"/>
       <c r="E17" s="11"/>
       <c r="F17" s="35"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18" s="4"/>
       <c r="C18" s="5"/>
-      <c r="D18" s="53"/>
+      <c r="D18" s="45"/>
       <c r="E18" s="11"/>
       <c r="F18" s="35"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19" s="4"/>
       <c r="C19" s="5"/>
-      <c r="D19" s="53"/>
+      <c r="D19" s="45"/>
       <c r="E19" s="11"/>
       <c r="F19" s="35"/>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20" s="4"/>
       <c r="C20" s="5"/>
-      <c r="D20" s="53"/>
+      <c r="D20" s="45"/>
       <c r="E20" s="11"/>
       <c r="F20" s="35"/>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21" s="4"/>
       <c r="C21" s="5"/>
-      <c r="D21" s="53"/>
+      <c r="D21" s="45"/>
       <c r="E21" s="11"/>
       <c r="F21" s="35"/>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22" s="4"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="53"/>
+      <c r="D22" s="45"/>
       <c r="E22" s="11"/>
       <c r="F22" s="35"/>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23" s="4"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="53"/>
+      <c r="D23" s="45"/>
       <c r="E23" s="11"/>
       <c r="F23" s="35"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24" s="4"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="53"/>
+      <c r="D24" s="45"/>
       <c r="E24" s="11"/>
       <c r="F24" s="35"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25" s="4"/>
       <c r="C25" s="5"/>
-      <c r="D25" s="53"/>
+      <c r="D25" s="45"/>
       <c r="E25" s="11"/>
       <c r="F25" s="35"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26" s="4"/>
       <c r="C26" s="5"/>
-      <c r="D26" s="53"/>
+      <c r="D26" s="45"/>
       <c r="E26" s="11"/>
       <c r="F26" s="35"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27" s="4"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="53"/>
+      <c r="D27" s="45"/>
       <c r="E27" s="11"/>
       <c r="F27" s="35"/>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28" s="4"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="53"/>
+      <c r="D28" s="45"/>
       <c r="E28" s="11"/>
       <c r="F28" s="35"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29" s="4"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="53"/>
+      <c r="D29" s="45"/>
       <c r="E29" s="11"/>
       <c r="F29" s="35"/>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30" s="4"/>
       <c r="C30" s="5"/>
-      <c r="D30" s="53"/>
+      <c r="D30" s="45"/>
       <c r="E30" s="11"/>
       <c r="F30" s="35"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B31" s="4"/>
       <c r="C31" s="5"/>
-      <c r="D31" s="53"/>
+      <c r="D31" s="45"/>
       <c r="E31" s="11"/>
       <c r="F31" s="35"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32" s="4"/>
       <c r="C32" s="5"/>
-      <c r="D32" s="53"/>
+      <c r="D32" s="45"/>
       <c r="E32" s="11"/>
       <c r="F32" s="35"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33" s="4"/>
       <c r="C33" s="5"/>
-      <c r="D33" s="53"/>
+      <c r="D33" s="45"/>
       <c r="E33" s="11"/>
       <c r="F33" s="35"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B34" s="4"/>
       <c r="C34" s="5"/>
-      <c r="D34" s="53"/>
+      <c r="D34" s="45"/>
       <c r="E34" s="11"/>
       <c r="F34" s="35"/>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B35" s="4"/>
       <c r="C35" s="5"/>
-      <c r="D35" s="53"/>
+      <c r="D35" s="45"/>
       <c r="E35" s="11"/>
       <c r="F35" s="35"/>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B36" s="4"/>
       <c r="C36" s="5"/>
-      <c r="D36" s="53"/>
+      <c r="D36" s="45"/>
       <c r="E36" s="11"/>
       <c r="F36" s="35"/>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B37" s="4"/>
       <c r="C37" s="5"/>
-      <c r="D37" s="53"/>
+      <c r="D37" s="45"/>
       <c r="E37" s="11"/>
       <c r="F37" s="35"/>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B38" s="4"/>
       <c r="C38" s="5"/>
-      <c r="D38" s="53"/>
+      <c r="D38" s="45"/>
       <c r="E38" s="11"/>
       <c r="F38" s="35"/>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B39" s="4"/>
       <c r="C39" s="5"/>
-      <c r="D39" s="53"/>
+      <c r="D39" s="45"/>
       <c r="E39" s="11"/>
       <c r="F39" s="35"/>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B40" s="4"/>
       <c r="C40" s="5"/>
-      <c r="D40" s="53"/>
+      <c r="D40" s="45"/>
       <c r="E40" s="11"/>
       <c r="F40" s="35"/>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B41" s="4"/>
       <c r="C41" s="5"/>
-      <c r="D41" s="53"/>
+      <c r="D41" s="45"/>
       <c r="E41" s="11"/>
       <c r="F41" s="35"/>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B42" s="4"/>
       <c r="C42" s="5"/>
-      <c r="D42" s="53"/>
+      <c r="D42" s="45"/>
       <c r="E42" s="11"/>
       <c r="F42" s="35"/>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B43" s="4"/>
       <c r="C43" s="5"/>
-      <c r="D43" s="53"/>
+      <c r="D43" s="45"/>
       <c r="E43" s="11"/>
       <c r="F43" s="35"/>
     </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B44" s="4"/>
       <c r="C44" s="5"/>
-      <c r="D44" s="53"/>
+      <c r="D44" s="45"/>
       <c r="E44" s="11"/>
       <c r="F44" s="35"/>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B45" s="4"/>
       <c r="C45" s="5"/>
-      <c r="D45" s="53"/>
+      <c r="D45" s="45"/>
       <c r="E45" s="11"/>
       <c r="F45" s="35"/>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B46" s="4"/>
       <c r="C46" s="5"/>
-      <c r="D46" s="53"/>
+      <c r="D46" s="45"/>
       <c r="E46" s="11"/>
       <c r="F46" s="35"/>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B47" s="4"/>
       <c r="C47" s="5"/>
-      <c r="D47" s="53"/>
+      <c r="D47" s="45"/>
       <c r="E47" s="11"/>
       <c r="F47" s="35"/>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B48" s="4"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="53"/>
+      <c r="D48" s="45"/>
       <c r="E48" s="11"/>
       <c r="F48" s="35"/>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B49" s="4"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="53"/>
+      <c r="D49" s="45"/>
       <c r="E49" s="11"/>
       <c r="F49" s="35"/>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B50" s="4"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="53"/>
+      <c r="D50" s="45"/>
       <c r="E50" s="11"/>
       <c r="F50" s="35"/>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B51" s="4"/>
       <c r="C51" s="5"/>
-      <c r="D51" s="53"/>
+      <c r="D51" s="45"/>
       <c r="E51" s="11"/>
       <c r="F51" s="35"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B52" s="4"/>
       <c r="C52" s="5"/>
-      <c r="D52" s="53"/>
+      <c r="D52" s="45"/>
       <c r="E52" s="11"/>
       <c r="F52" s="35"/>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B53" s="4"/>
       <c r="C53" s="5"/>
-      <c r="D53" s="53"/>
+      <c r="D53" s="45"/>
       <c r="E53" s="11"/>
       <c r="F53" s="35"/>
     </row>
-    <row r="54" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B54" s="4"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="53"/>
+      <c r="D54" s="45"/>
       <c r="E54" s="11"/>
       <c r="F54" s="35"/>
     </row>
-    <row r="55" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B55" s="4"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="53"/>
+      <c r="D55" s="45"/>
       <c r="E55" s="4"/>
       <c r="F55" s="35"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="Df2OUiSxaRu36BSW5+FG1qH4flp1NKafA7aNQIbLZFzuDRbtm5QBNUDvW9LmxUUbJ0m5Bw0wj0DPzqloK/S9EA==" saltValue="bXAj5LSi83tUYecmG5EhMw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
-  <mergeCells count="5">
+  <sheetProtection algorithmName="SHA-512" hashValue="buB3V9UQB2uN3z1tYPqa5vQ6bsQK9iiijw/gELP6qKJFHjriwEk/FFLSLF1u7TpNPxfx7PsuF5DKpjrqSzHs0g==" saltValue="K/+3Wr8U36/+vohpPcQGGw==" spinCount="100000" sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
+  <mergeCells count="3">
     <mergeCell ref="B4:C4"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="J4:L4"/>
-    <mergeCell ref="M4:O4"/>
-    <mergeCell ref="B2:O3"/>
+    <mergeCell ref="B2:K3"/>
   </mergeCells>
-  <conditionalFormatting sqref="B6:O1048576">
+  <conditionalFormatting sqref="B6:K1048576">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>B6=""</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5:C5 E5 D5" xr:uid="{4028DFA7-3B9E-4D78-9BE4-B9C30D52F4E5}">
       <formula1>"&lt;0&gt;0"</formula1>
     </dataValidation>
